--- a/out/Attention-S4_repeat_4_000006.xlsx
+++ b/out/Attention-S4_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.5730533708028094</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>2.544994382064366</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC44" t="n">
-        <v>-2.354090312181506e-05</v>
+        <v>-0.0003232642297846032</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.03029897606577552</v>
+        <v>0.4160660343422569</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.06065529236892122</v>
+        <v>0.8329198876453278</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.006997308416314641</v>
+        <v>-0.09608684619637914</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.3196559239160933</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.3196559239160933</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.02323323840350448</v>
+        <v>0.3193076530519645</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1379066971591628</v>
+        <v>1.069963414907334</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2993212371885206</v>
+        <v>2.461365030106046</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02638689261650664</v>
+        <v>0.2047253813686029</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2139870774266776</v>
+        <v>1.79929110009346</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04621914490029407</v>
+        <v>0.3585961387678064</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2800514092625996</v>
+        <v>2.311858226935436</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02531104742762921</v>
+        <v>0.1963802951163542</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2844149980685517</v>
+        <v>2.345713590195723</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01045281497319383</v>
+        <v>0.08110792182572622</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6660834373006792</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2799839799202834</v>
+        <v>2.311343270965822</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01302391128671369</v>
+        <v>0.1010530199618761</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>5.653970270522433</v>
+        <v>1.944994382064366</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2955809793231609</v>
+        <v>2.432355984321626</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0078406353126978</v>
+        <v>0.0608475618672416</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.298230286189219</v>
+        <v>2.452928532092454</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.005959737115963157</v>
+        <v>0.04626050456281997</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3023064439572864</v>
+        <v>2.4845759784433</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002633224828833108</v>
+        <v>0.02046034716589962</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3016089492075231</v>
+        <v>2.479196957361995</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002088435805000613</v>
+        <v>0.01623543955211618</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3031518361160296</v>
+        <v>2.491201054636001</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001033114309271595</v>
+        <v>0.008049766447842251</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3031283083520914</v>
+        <v>2.491052297045925</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0005972045543453149</v>
+        <v>0.004678813200463561</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3032919658556806</v>
+        <v>2.492355902660127</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.00233690660023178</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3032865891519438</v>
+        <v>2.492347986828319</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001444817044438485</v>
+        <v>0.001150608561277444</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3032778051727461</v>
+        <v>2.492313699164271</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.177897222547117e-05</v>
+        <v>0.0006658682083584501</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>5.053970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3032968027792545</v>
+        <v>2.492494682683167</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>0.0002204289815111627</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3032629839807705</v>
+        <v>2.492265782787252</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.474746883626259e-06</v>
+        <v>0.0001072895573635522</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3032581469194502</v>
+        <v>2.49226203913357</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>5.615490325271265e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3032545422421196</v>
+        <v>2.492267195420259</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>2.58123458105224e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3032492318649737</v>
+        <v>2.492260177968811</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3032453075786226</v>
+        <v>2.492262171918604</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3032449754752994</v>
+        <v>2.49225483752446</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3032453560103571</v>
+        <v>2.492251352304153</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3032455843313919</v>
+        <v>2.492246804991967</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3032456742760418</v>
+        <v>2.492246894936617</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.303244816342457</v>
+        <v>2.492246037003032</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3032450446634917</v>
+        <v>2.492246265324067</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3032442489992799</v>
+        <v>2.492245469659855</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.303244311268653</v>
+        <v>2.492245531929228</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3032443389439299</v>
+        <v>2.492245559604505</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3032444911579532</v>
+        <v>2.492245711818528</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3032441452169914</v>
+        <v>2.492245365877567</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3032442213240031</v>
+        <v>2.492245441984578</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3032443873756647</v>
+        <v>2.49224560803624</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3032447471542647</v>
+        <v>2.49224596781484</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3032447679107224</v>
+        <v>2.492245988571298</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3032448716930109</v>
+        <v>2.492246092353586</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3032451000140456</v>
+        <v>2.492246320674621</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3032449754752994</v>
+        <v>2.492246196135875</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3032450031505763</v>
+        <v>2.492246223811152</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3032450585011302</v>
+        <v>2.492246279161705</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3032453214162609</v>
+        <v>2.492246542076836</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3032452383904301</v>
+        <v>2.492246459051005</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3032450308258534</v>
+        <v>2.492246251486429</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3032450446634917</v>
+        <v>2.492246265324067</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3032451830398764</v>
+        <v>2.492246403700452</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3032448993682877</v>
+        <v>2.492246120028863</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.303244726397807</v>
+        <v>2.492245947058382</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3032446226155185</v>
+        <v>2.492245843276094</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3032447679107224</v>
+        <v>2.492245988571298</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3032450100693956</v>
+        <v>2.492246230729971</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3032448370989146</v>
+        <v>2.49224605775949</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3032445395896877</v>
+        <v>2.492245760250263</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3032445257520492</v>
+        <v>2.492245746412625</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.30324415905463</v>
+        <v>2.492245379715205</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.30324415905463</v>
+        <v>2.492245379715205</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3032440967852569</v>
+        <v>2.492245317445832</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3032439930029684</v>
+        <v>2.492245213663544</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3032438200324876</v>
+        <v>2.492245040693063</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3032438684642222</v>
+        <v>2.492245089124797</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3032435086856221</v>
+        <v>2.492244729346198</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3032434671727067</v>
+        <v>2.492244687833282</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3032435225232604</v>
+        <v>2.492244743183836</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3032435778738144</v>
+        <v>2.49224479853439</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3032436193867298</v>
+        <v>2.492244840047305</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3032433495527797</v>
+        <v>2.492244570213355</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3032434049033336</v>
+        <v>2.492244625563909</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3032435501985375</v>
+        <v>2.492244770859113</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3032435156044413</v>
+        <v>2.492244736265017</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3032435017668028</v>
+        <v>2.492244722427378</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3032435917114529</v>
+        <v>2.492244812372028</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>5.653970270522433</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3032439099771376</v>
+        <v>2.492245130637713</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3032437300878374</v>
+        <v>2.492244950748413</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3032437716007528</v>
+        <v>2.492244992261328</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3032435847926335</v>
+        <v>2.492244805453209</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.303243653980826</v>
+        <v>2.492244874641401</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3032434533350682</v>
+        <v>2.492244673995644</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3032434948479836</v>
+        <v>2.492244715508559</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-1.173053370802809</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3032435225232604</v>
+        <v>2.492244743183836</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000006.xlsx
+++ b/out/Attention-S4_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC44" t="n">
-        <v>-2.354090312181506e-05</v>
+        <v>-6.659310143790208e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.03029897606577552</v>
+        <v>0.08571029844151974</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.06065529236892122</v>
+        <v>0.1715832238811925</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.006997308416314641</v>
+        <v>-0.019794128089013</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.06584957725106878</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.02327812674633902</v>
+        <v>0.06584957725106878</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.02323323840350448</v>
+        <v>0.06576913313045958</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1379066971591628</v>
+        <v>0.2471417361066037</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2993212371885206</v>
+        <v>0.5605447223041812</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02638689261650664</v>
+        <v>0.04728778649651451</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2139870774266776</v>
+        <v>0.4076179041932386</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04621914490029407</v>
+        <v>0.08282882519530735</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2800514092625996</v>
+        <v>0.5260113836760975</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02531104742762921</v>
+        <v>0.04536031712922705</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2844149980685517</v>
+        <v>0.5338313638482525</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01045281497319383</v>
+        <v>0.0187344715697044</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2799839799202834</v>
+        <v>0.5258924381063527</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01302391128671369</v>
+        <v>0.02334105347173814</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2955809793231609</v>
+        <v>0.5538441996335457</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0078406353126978</v>
+        <v>0.01405452026894445</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.298230286189219</v>
+        <v>0.5585957655069235</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.005959737115963157</v>
+        <v>0.01068301840447736</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.3023064439572864</v>
+        <v>0.5659042751258812</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002633224828833108</v>
+        <v>0.004723143895047287</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.3016089492075231</v>
+        <v>0.5646582077279626</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002088435805000613</v>
+        <v>0.003745528966308327</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>5.653970270522433</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.3031518361160296</v>
+        <v>0.5674272837359675</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001033114309271595</v>
+        <v>0.001856101315898955</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>5.653970270522433</v>
+        <v>3.04</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.3031283083520914</v>
+        <v>0.5673890676965215</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0005972045543453149</v>
+        <v>0.001077222677374189</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>5.653970270522433</v>
+        <v>3.04</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3032919658556806</v>
+        <v>0.5676864287452689</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.0005361113386870947</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>5.653970270522433</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3032865891519438</v>
+        <v>0.5676807550251242</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001444817044438485</v>
+        <v>0.0002623422791014983</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.06608343730067928</v>
+        <v>1.996323785759845</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3032778051727461</v>
+        <v>0.5676689875238669</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.177897222547117e-05</v>
+        <v>0.0001485320277835259</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>5.053970270522433</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3032968027792545</v>
+        <v>0.5677069083885781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>4.633531262135388e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.7526475715196894</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3032629839807705</v>
+        <v>0.5676498142724908</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.474746883626259e-06</v>
+        <v>2.194949376725252e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3032581469194502</v>
+        <v>0.5676451124745737</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3032545422421196</v>
+        <v>0.5676425018283974</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3032492318649737</v>
+        <v>0.5676370362626785</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3032453075786226</v>
+        <v>0.5676336516442275</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3032449754752994</v>
+        <v>0.5676279842139539</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3032453560103571</v>
+        <v>0.5676283647490116</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3032455843313919</v>
+        <v>0.5676285930700463</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3032456742760418</v>
+        <v>0.5676286830146963</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.303244816342457</v>
+        <v>0.5676278250811114</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3032450446634917</v>
+        <v>0.5676280534021461</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3032442489992799</v>
+        <v>0.5676272577379343</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.303244311268653</v>
+        <v>0.5676273200073074</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3032443389439299</v>
+        <v>0.5676273476825843</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3032444911579532</v>
+        <v>0.5676274998966075</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3032441452169914</v>
+        <v>0.5676271539556459</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3032442213240031</v>
+        <v>0.5676272300626575</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3032443873756647</v>
+        <v>0.5676273961143191</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3032447471542647</v>
+        <v>0.5676277558929191</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3032447679107224</v>
+        <v>0.5676277766493768</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3032448716930109</v>
+        <v>0.5676278804316653</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3032451000140456</v>
+        <v>0.5676281087527001</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3032449754752994</v>
+        <v>0.5676279842139539</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3032450031505763</v>
+        <v>0.5676280118892307</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3032450585011302</v>
+        <v>0.5676280672397847</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3032453214162609</v>
+        <v>0.5676283301549153</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3032452383904301</v>
+        <v>0.5676282471290846</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3032450308258534</v>
+        <v>0.5676280395645078</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3032450446634917</v>
+        <v>0.5676280534021461</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3032451830398764</v>
+        <v>0.5676281917785309</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3032448993682877</v>
+        <v>0.5676279081069422</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.303244726397807</v>
+        <v>0.5676277351364615</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3032446226155185</v>
+        <v>0.5676276313541729</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3032447679107224</v>
+        <v>0.5676277766493768</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3032450100693956</v>
+        <v>0.56762801880805</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3032448370989146</v>
+        <v>0.5676278458375691</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3032445395896877</v>
+        <v>0.5676275483283422</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3032445257520492</v>
+        <v>0.5676275344907036</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.30324415905463</v>
+        <v>0.5676271677932844</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.30324415905463</v>
+        <v>0.5676271677932844</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3032440967852569</v>
+        <v>0.5676271055239113</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3032439930029684</v>
+        <v>0.5676270017416228</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3032438200324876</v>
+        <v>0.567626828771142</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3032438684642222</v>
+        <v>0.5676268772028766</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3032435086856221</v>
+        <v>0.5676265174242766</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3032434671727067</v>
+        <v>0.5676264759113612</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3032435225232604</v>
+        <v>0.5676265312619149</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3032435778738144</v>
+        <v>0.5676265866124688</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3032436193867298</v>
+        <v>0.5676266281253842</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3032433495527797</v>
+        <v>0.5676263582914342</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3032434049033336</v>
+        <v>0.5676264136419881</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3032435501985375</v>
+        <v>0.5676265589371919</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3032435156044413</v>
+        <v>0.5676265243430957</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3032435017668028</v>
+        <v>0.5676265105054572</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6660834373006792</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3032435917114529</v>
+        <v>0.5676266004501074</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>5.653970270522433</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3032439099771376</v>
+        <v>0.567626918715792</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.06608343730067928</v>
+        <v>0.9526475715196895</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3032437300878374</v>
+        <v>0.5676267388264918</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.06608343730067928</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3032437716007528</v>
+        <v>0.5676267803394073</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.09102864272046574</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3032435847926335</v>
+        <v>0.567626593531288</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.303243653980826</v>
+        <v>0.5676266627194805</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3032434533350682</v>
+        <v>0.5676264620737226</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3032434948479836</v>
+        <v>0.567626503586638</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6660834373006792</v>
+        <v>-0.2910286427204658</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3032435225232604</v>
+        <v>0.5676265312619149</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000006.xlsx
+++ b/out/Attention-S4_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.004454849287867546</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.003373537212610245</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003452802076935768</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.00297868438065052</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.004009971395134926</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.004419634118676186</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003846677020192146</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003805192187428474</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.003912961110472679</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.005354402586817741</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.005734829232096672</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.005397351458668709</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.00603313185274601</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.006710654124617577</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.00678815133869648</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.007148182019591331</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.007395684719085693</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.00751923955976963</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.007489224895834923</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.007741721346974373</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00799640454351902</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.008111214265227318</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008131608366966248</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.008000392466783524</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.008768441155552864</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.007558297365903854</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002809502184391022</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.007860321551561356</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.008127184584736824</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.00840395875275135</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.008102891966700554</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.007464507594704628</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.007975341752171516</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.006953848525881767</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.00874692015349865</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.008943570777773857</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.008008413016796112</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.006824532523751259</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.005799021571874619</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.006240945309400558</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.006317416206002235</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.005453787744045258</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0007463134825229645</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.659310143790208e-05</v>
+        <v>-0.0001987187176558655</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08571029844151974</v>
+        <v>0.2557662586041952</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001363847404718399</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1715832238811925</v>
+        <v>0.5120169718848381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.019794128089013</v>
+        <v>-0.05906703913986523</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.006677271798253059</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06584957725106878</v>
+        <v>0.1965005007466741</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.004645764827728271</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06584957725106878</v>
+        <v>0.1965005007466741</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.004748443141579628</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06576913313045958</v>
+        <v>0.1963828673377773</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2471417361066037</v>
+        <v>0.3613951103598632</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.005912313237786293</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5605447223041812</v>
+        <v>0.9198930353748644</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.04728778649651451</v>
+        <v>0.0691489443891683</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001749202609062195</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4076179041932386</v>
+        <v>0.6962681033441495</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08282882519530735</v>
+        <v>0.1211209340514027</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.00285409577190876</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5260113836760975</v>
+        <v>0.8693949233385578</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04536031712922705</v>
+        <v>0.06633023114948934</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001449910923838615</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5338313638482525</v>
+        <v>0.880830052659319</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0187344715697044</v>
+        <v>0.02739535145095675</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003648532554507256</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5258924381063527</v>
+        <v>0.8692209896530213</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02334105347173814</v>
+        <v>0.03413225699722719</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.00362733006477356</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5538441996335457</v>
+        <v>0.9100947503836011</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01405452026894445</v>
+        <v>0.02055143706425703</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002756133675575256</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.996323785759845</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5585957655069235</v>
+        <v>0.9170433875449591</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01068301840447736</v>
+        <v>0.01562548581592755</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01159003935754299</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9526475715196895</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5659042751258812</v>
+        <v>0.9277329877203163</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004723143895047287</v>
+        <v>0.006908420485195193</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.008950615301728249</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.996323785759845</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5646582077279626</v>
+        <v>0.9259133177435275</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003745528966308327</v>
+        <v>0.005480810693826908</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.00048077292740345</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.996323785759845</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5674272837359675</v>
+        <v>0.9299645274134087</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001856101315898955</v>
+        <v>0.002714109046212586</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.02045479975640774</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.04</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5673890676965215</v>
+        <v>0.9299109773089972</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001077222677374189</v>
+        <v>0.00157760520562247</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01182684488594532</v>
       </c>
       <c r="JB60" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5676864287452689</v>
+        <v>0.930348139702864</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005361113386870947</v>
+        <v>0.0007863026028112352</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0006786677986383438</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.996323785759845</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5676807550251242</v>
+        <v>0.9303421544777064</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002623422791014983</v>
+        <v>0.0003859521500839116</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001021226868033409</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.996323785759845</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5676689875238669</v>
+        <v>0.9303272579167278</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0.0002219603888973861</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.004368852823972702</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7526475715196894</v>
+        <v>-0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5677069083885781</v>
+        <v>0.9303850208875958</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00355539470911026</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7526475715196894</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5676498142724908</v>
+        <v>0.9303046486454069</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.194949376725252e-05</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002739371731877327</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5676451124745737</v>
+        <v>0.9303000710983579</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>1.456956904086805e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.004258623346686363</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5676425018283974</v>
+        <v>0.9302984575492137</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.003225076943635941</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5676370362626785</v>
+        <v>0.9302927606879102</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001281818374991417</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5676336516442275</v>
+        <v>0.9302904517831083</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003928553313016891</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5676279842139539</v>
+        <v>0.9302844522495116</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002753155305981636</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5676283647490116</v>
+        <v>0.9302802096393576</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.004949091002345085</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5676285930700463</v>
+        <v>0.9302804379603923</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003452686592936516</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5676286830146963</v>
+        <v>0.9302805279050422</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004509175196290016</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5676278250811114</v>
+        <v>0.9302796699714575</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002995697781443596</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5676280534021461</v>
+        <v>0.9302798982924921</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003969224169850349</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5676272577379343</v>
+        <v>0.9302791026282804</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006471367552876472</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5676273200073074</v>
+        <v>0.9302791648976535</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.005560683086514473</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5676273476825843</v>
+        <v>0.9302791925729303</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004613835364580154</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5676274998966075</v>
+        <v>0.9302793447869536</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.006295660510659218</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5676271539556459</v>
+        <v>0.930278998845992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005768280476331711</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5676272300626575</v>
+        <v>0.9302790749530035</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006358025595545769</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5676273961143191</v>
+        <v>0.9302792410046652</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004595799371600151</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5676277558929191</v>
+        <v>0.9302796007832652</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003345254808664322</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5676277766493768</v>
+        <v>0.9302796215397229</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003362266346812248</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5676278804316653</v>
+        <v>0.9302797253220114</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005480421707034111</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5676281087527001</v>
+        <v>0.9302799536430461</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.00518486462533474</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5676279842139539</v>
+        <v>0.9302798291042998</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.005359688773751259</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5676280118892307</v>
+        <v>0.9302798567795767</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.004467586055397987</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5676280672397847</v>
+        <v>0.9302799121301307</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.004992956295609474</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5676283301549153</v>
+        <v>0.9302801750452614</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.004283493384718895</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5676282471290846</v>
+        <v>0.9302800920194306</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004992339760065079</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5676280395645078</v>
+        <v>0.9302798844548539</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005630938336253166</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5676280534021461</v>
+        <v>0.9302798982924921</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005537096410989761</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5676281917785309</v>
+        <v>0.9302800366688769</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.00573732890188694</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5676279081069422</v>
+        <v>0.9302797529972883</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.005529057234525681</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5676277351364615</v>
+        <v>0.9302795800268076</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004692474380135536</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5676276313541729</v>
+        <v>0.930279476244519</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005620783194899559</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5676277766493768</v>
+        <v>0.9302796215397229</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005115309730172157</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.56762801880805</v>
+        <v>0.9302798636983961</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005321873351931572</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5676278458375691</v>
+        <v>0.9302796907279152</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003625182434916496</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5676275483283422</v>
+        <v>0.9302793932186882</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005000097677111626</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5676275344907036</v>
+        <v>0.9302793793810497</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004536429420113564</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5676271677932844</v>
+        <v>0.9302790126836304</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.004761198535561562</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5676271677932844</v>
+        <v>0.9302790126836304</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002753857523202896</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5676271055239113</v>
+        <v>0.9302789504142573</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004495561122894287</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5676270017416228</v>
+        <v>0.9302788466319689</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00487164780497551</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.567626828771142</v>
+        <v>0.9302786736614881</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004499536007642746</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5676268772028766</v>
+        <v>0.9302787220932227</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004997933283448219</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5676265174242766</v>
+        <v>0.9302783623146226</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004920968785881996</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5676264759113612</v>
+        <v>0.9302783208017072</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004485350102186203</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5676265312619149</v>
+        <v>0.9302783761522609</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004787459969520569</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5676265866124688</v>
+        <v>0.9302784315028149</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004993336275219917</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5676266281253842</v>
+        <v>0.9302784730157303</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.00685092993080616</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5676263582914342</v>
+        <v>0.9302782031817802</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.006792526692152023</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5676264136419881</v>
+        <v>0.9302782585323341</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.005108101293444633</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5676265589371919</v>
+        <v>0.930278403827538</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004754466935992241</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5676265243430957</v>
+        <v>0.9302783692334418</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003675417974591255</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5676265105054572</v>
+        <v>0.9302783553958033</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002343056723475456</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5676266004501074</v>
+        <v>0.9302784453404535</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.003560012206435204</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.567626918715792</v>
+        <v>0.930278763606138</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001622548326849937</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9526475715196895</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5676267388264918</v>
+        <v>0.9302785837168379</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002580763772130013</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5676267803394073</v>
+        <v>0.9302786252297534</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00208999402821064</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.09102864272046574</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.567626593531288</v>
+        <v>0.930278438421634</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001964740455150604</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2910286427204658</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5676266627194805</v>
+        <v>0.9302785076098266</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002649189904332161</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5676264620737226</v>
+        <v>0.9302783069640687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004677673801779747</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.4400000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.567626503586638</v>
+        <v>0.9302783484769841</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003791604191064835</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.2910286427204658</v>
+        <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5676265312619149</v>
+        <v>0.9302783761522609</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000006.xlsx
+++ b/out/Attention-S4_repeat_4_000006.xlsx
@@ -51029,7 +51029,7 @@
         <v>0.004368852823972702</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0.9303850208875958</v>
@@ -51824,7 +51824,7 @@
         <v>-0.00355539470911026</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0.9303046486454069</v>
@@ -52619,7 +52619,7 @@
         <v>-0.002739371731877327</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0.9303000710983579</v>
@@ -53414,7 +53414,7 @@
         <v>-0.004258623346686363</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0.9302984575492137</v>
@@ -54209,7 +54209,7 @@
         <v>-0.003225076943635941</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0.9302927606879102</v>
